--- a/docs/Reports/Enhancement_Requests.xlsx
+++ b/docs/Reports/Enhancement_Requests.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="40">
   <si>
     <t xml:space="preserve">Enhancement suggestions</t>
   </si>
@@ -127,7 +127,227 @@
     <t xml:space="preserve">Enc_02</t>
   </si>
   <si>
+    <t xml:space="preserve">Cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provide a visible counter on how many times the product is added to the cart</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on a product  
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Click add to cart 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Return to homepage and repeat steps 1 and 2 for the same product</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">.
+ 4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on cart from navbar</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Users should see a visible and adjustable counter of how many entries the product has in their cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The UI gets clogged with multiple entries of the same product which results in the user having to scroll up and down his cart while still looking at the same product.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CART-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It would serve for a more user friendly interface, while also removing the need for the user to personally count how many times a product has been added to cart.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Enc_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Products in cart are shuffling their positions on refresh
+</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1.  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on a product </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click add to cart</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Return to homepage and repeat steps 1 and 2 for a different product.</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> 
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Click on cart from navbar
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Refresh the page multiple times</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">The products should stay in a specific order.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The products places are randomized after each refresh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CART-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Might confuse the user.
+Must be clarified which exact type of ordering is to be used.</t>
   </si>
   <si>
     <t xml:space="preserve">Enc_04</t>
@@ -146,11 +366,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -170,12 +391,6 @@
     <font>
       <b val="true"/>
       <sz val="22"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
@@ -270,49 +485,45 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -501,187 +712,223 @@
   <dimension ref="A1:L9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="95.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="2"/>
+      <c r="L2" s="3"/>
     </row>
-    <row r="3" customFormat="false" ht="173.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="5" t="s">
+    <row r="3" customFormat="false" ht="104.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="2"/>
+      <c r="L3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2"/>
-      <c r="B4" s="5" t="s">
+    <row r="4" customFormat="false" ht="173.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3"/>
+      <c r="B4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="2"/>
+      <c r="C4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="5" t="s">
+    <row r="5" customFormat="false" ht="196.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3"/>
+      <c r="B5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="2"/>
+      <c r="D5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="2"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="2"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="2"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="1">
